--- a/_s4/NEMI_website_update_list.xlsx
+++ b/_s4/NEMI_website_update_list.xlsx
@@ -546,7 +546,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Live site nemilmm.com read page by page on 28 Sep 2026, 15 pages, 47 images, 14 videos, checked against the website plan of 18 Sep 2026 and the vShare investor deck of Aug 2026. 44 items. Fill the two cream columns.</t>
+          <t>Live site nemilmm.com read page by page on 28 Sep 2026, 15 pages, 47 images, 14 videos, checked against the website plan of 18 Sep 2026 and the vShare investor deck of Aug 2026. 44 items. 22 now fixed on the BCA-Ready branch as of 28 Sep 2026, none of them live yet. Fill the two cream columns.</t>
         </is>
       </c>
     </row>
@@ -1386,10 +1386,14 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr"/>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Orphan asterisk removed from the case-studies card. The figures themselves still need the evidence pack.</t>
+        </is>
+      </c>
       <c r="L19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1488,12 +1492,16 @@
           <t>CTO</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Now 'on the parts we design, tool and ship'.</t>
+        </is>
+      </c>
       <c r="L21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1698,10 +1706,14 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr"/>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Section retitled 'The Markets We Build For' so it no longer reads as delivered work. The image itself is still third-party and still needs replacing or licensing.</t>
+        </is>
+      </c>
       <c r="L25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1750,10 +1762,14 @@
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr"/>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Same retitle covers the implied-customer problem. Licensing still open.</t>
+        </is>
+      </c>
       <c r="L26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1904,12 +1920,16 @@
           <t>Counsel</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr"/>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Removed from about, contact and FAQ.</t>
+        </is>
+      </c>
       <c r="L29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2164,12 +2184,16 @@
           <t>Counsel</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="inlineStr"/>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>Now 'we intend to be part of it'.</t>
+        </is>
+      </c>
       <c r="L34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2216,12 +2240,16 @@
           <t>CTO</t>
         </is>
       </c>
-      <c r="J35" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="inlineStr"/>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>'Proven daily' is now 'run daily'.</t>
+        </is>
+      </c>
       <c r="L35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2320,12 +2348,16 @@
           <t>COO</t>
         </is>
       </c>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr"/>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>Now reads 'on a recent programme', so it is an instance not a standing capability.</t>
+        </is>
+      </c>
       <c r="L37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2476,12 +2508,16 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr"/>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>Standardised to '24 to 48 hours' across home, FAQ, offerings and contact. Tighten it if sales can commit to 24.</t>
+        </is>
+      </c>
       <c r="L40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
@@ -2580,12 +2616,16 @@
           <t>CTO</t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr"/>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>Now 'each unit shipped adds to what the model has seen'.</t>
+        </is>
+      </c>
       <c r="L42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2840,12 +2880,16 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr"/>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>Alt text written for all six, plus the offerings collage.</t>
+        </is>
+      </c>
       <c r="L47" s="7" t="inlineStr"/>
     </row>
     <row r="48">

--- a/_s4/NEMI_website_update_list.xlsx
+++ b/_s4/NEMI_website_update_list.xlsx
@@ -1176,12 +1176,16 @@
           <t>CFO</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>The unsourced $10M+ benchmark and the 90% delta are gone site-wide. Our own &lt;$1M stays. The site-versus-deck reconciliation is still open.</t>
+        </is>
+      </c>
       <c r="L15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1280,12 +1284,16 @@
           <t>Sales + CFO</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Customer-supplied cost benchmark withheld pending written consent. Our own ~$100k and the delivery facts stay.</t>
+        </is>
+      </c>
       <c r="L17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
@@ -2080,12 +2088,16 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr"/>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>Swapped for care-robotics.jpg, our own robotics cell.</t>
+        </is>
+      </c>
       <c r="L32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2296,12 +2308,16 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="inlineStr"/>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>Headline is now 'Programmes we have delivered'; kicker matches.</t>
+        </is>
+      </c>
       <c r="L36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2564,12 +2580,16 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="inlineStr"/>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>Swapped for our own: fac-assembly.jpg and care-floor-cad.jpg.</t>
+        </is>
+      </c>
       <c r="L41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2672,12 +2692,16 @@
           <t>Counsel</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="inlineStr"/>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>Now 'we hold ourselves to the committed date'. No longer phrased as a contract term.</t>
+        </is>
+      </c>
       <c r="L43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2724,12 +2748,16 @@
           <t>COO</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr"/>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>Multiple dropped; reads 'faster to first shot' until a benchmark exists.</t>
+        </is>
+      </c>
       <c r="L44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
@@ -2776,12 +2804,16 @@
           <t>Quality</t>
         </is>
       </c>
-      <c r="J45" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr"/>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>Now 'built to MIL-STD-810 / 461 requirements where a programme calls for them'.</t>
+        </is>
+      </c>
       <c r="L45" s="7" t="inlineStr"/>
     </row>
     <row r="46">

--- a/_s4/NEMI_website_update_list.xlsx
+++ b/_s4/NEMI_website_update_list.xlsx
@@ -1044,27 +1044,27 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>NEMI carbon-fibre defense UAS photograph</t>
+          <t>Defense UAS hero: an AI-generated illustration, captioned as the delivered airframe</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Customer property</t>
+          <t>Misleading image</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>A defence customer's airframe published without written consent</t>
+          <t>Not customer property after all: the render is ours. But it read as a photograph of delivered hardware</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Get consent or replace the image</t>
+          <t>Labelled as an illustration on the case page and the index card</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1072,12 +1072,16 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Fixed on branch</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Confirmed with the CEO on 28 Sep 2026 that the image is AI-generated and illustrative.</t>
+        </is>
+      </c>
       <c r="L13" s="7" t="inlineStr"/>
     </row>
     <row r="14">

--- a/_s4/NEMI_website_update_list.xlsx
+++ b/_s4/NEMI_website_update_list.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Vinod Dasari, Ramesh Mangaleswaran, Sampath Ravinarayanan, Naoya Nishimura, Sam Swaminathan</t>
+          <t>Board and leadership structure</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Titles and roles differ from the deck; the S-4 lists directors exactly, and family relationships must be disclosed</t>
+          <t>The S-4 lists directors and officers exactly. The site now names four directors and seven officers</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Confirm each seat, title and any family relationship</t>
+          <t>Structure updated 28 Sep. Still to confirm: each director's formal appointment, and any family relationship among directors and officers</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -760,12 +760,16 @@
           <t>CEO + counsel</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Board: Anirudh, Sam Swaminathan, Jingjing Kanik (ind.), Manoj Ganesh (ind.). Leadership: 7. Bios from LinkedIn, need sign-off from each person.</t>
+        </is>
+      </c>
       <c r="L7" s="7" t="inlineStr"/>
     </row>
     <row r="8">

--- a/_s4/NEMI_website_update_list.xlsx
+++ b/_s4/NEMI_website_update_list.xlsx
@@ -800,10 +800,14 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Fixed on branch</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="n"/>
+          <t>Reverted on branch</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>5 Oct: Master Plan page restored to the live wording on request, so the letter carries this again. About keeps the softened text.</t>
+        </is>
+      </c>
       <c r="L8" s="6" t="n"/>
     </row>
     <row r="9">
@@ -852,10 +856,14 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Fixed on branch</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="n"/>
+          <t>Reverted on branch</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>5 Oct: Master Plan page restored to the live wording on request, so the letter carries this again. About keeps the softened text.</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="n"/>
     </row>
     <row r="10" ht="22.5" customHeight="1">
